--- a/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
+++ b/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -531,63 +531,67 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr"/>
+          <t>복지</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
+          <t>2026년 한국법무보호복지공단 서울지부 취업지원직(육아휴직대체직) 경력경쟁채용시험 공고</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>무기계약직,비정규직</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
+          <t>학력무관</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-3</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
+          <t>- 임용예정일에 근무가 가능한 자 - 공고일 기준 만 18세 이상 및 만 60세 이하(공단 정년) - 남성의 경우 「병역법」에 따라 병역의무 불이행 사실이 없는 자 - 성별 ? 학력 ? 거주지 제한 없음 - 공단 규정에 따라 비상대기 및 출동 가능한 자 - 공단 인사규정 등에 의한 임용결격사유에 해당되지 않는 자 [취업지원직 자격요건] 아래 자격증 중 1개 이상 취득한 자 ①직업상담사 2급 이상 ②사회복지사 2급 이상 ③청소년상담사 2급 이상</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
+          <t>가. 장애인 : 서류전형 만점의 5% - 「장애인 고용촉진 및 직업재활법 시행령」에 의한 장애인 나. 공단 체험형 청년인턴 : 서류전형 만점의 1% ~ 2% - 우리 공단 체험형 청년인턴으로 6개월 이상 근무하여 수료한 경우 수료일로부터 2년 이내 서류전형 만점의 2%(공고문 참고) 다. 가산특전 적용 유의사항 - 가산특전은 서류전형 점수에만 적용 - 장애인 가산특전은 타 가산특전과 중복 적용 가능 - 응시자의 서류전형 점수가 만점의 40% 미만일 경우 적용 제외 - 세부 참조 사항은 공고문 참조 장애인, 한국법무보호복지공단 체험형</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -597,70 +601,74 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+          <t>https://recruit.incruit.com/koreha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
+          <t>복지 · 행정</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>2026년 한국법무보호복지공단 신입직원 공개(경력)경쟁채용시험 공고</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
+          <t>서울,부산,대구,인천,대전,울산,경기,강원,충북,충남,전북,전남광주,경북,경남,제주</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>학력무관,대졸(4년)</t>
+          <t>학력무관</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
+          <t>&lt;공통 응시자격&gt; - 임용예정일에 근무 가능한 자 - 만 18세 이상 및 60세 이하(공단 정년) - 남성의 경우, 「병역법」에 따라 병역의무 불이행 사실이 없는 자 - 성별 · 학력 · 거주지 제한 없음 - 공단 규정에 따라 전국 순환근무, 비상대기 · 출동 가능한 자 - 공단 인사규정 등에 의한 임용결격사유에 해당되지 않는 자 ※【별첨 1】임용 결격사유 &lt;심리상담직&gt; - 다음 자격증 중 1개 이상의 자격증을 취득한 사람 ① 정신건강임상심리사 2급 이상 ② 상담심리사 2급 이상(※ 한국상담심리학회) ③ 임상심리사 2급 이상 ④ 전문상담사 2급 이상(※ 한국상담학회) &lt;취업지원직&gt; - 다음 자격증 중 1개 이상의 자격증을 취득하고, 이후 취업지원업무 수행 경력 1년 이상인 자 ① 직업상담사 2급 이상 ② 사회복지사 2급 이상 ③ 청소년상담사 2급 이상 &lt;직업훈련교사직(전기)&gt; - 「국민평생직업능력개발법」 제33조에 따른 직업능력개발훈련교사 3급(전기·전기공사) 이상 소지자</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
+          <t>가산특전 1) 취업지원대상자 : 5% 또는 10%로 보호직(전국), 취업지원직 모집에 한함 2) 직무관련자격증 : 3% 또는 5%로 보호직에만 적용 3) 장애인 : 5%로 전 채용분야에 적용 4) 한국사능력검정시험 등급 소지자 : 1% 또는 1.5% 또는 2%로 전 채용분야에 적용 5) 한국법무보호복지공단 체험형 청년인턴 : 1% 또는 2%로 전 채용분야에 적용 * 상세사항 공고문 참조 업지원대상자, 직무 관련 자격증, 장애인, 한국사능력검정시험 등급 소지자, 한국법무보호복지공단 체험형 청년인턴 경력</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -670,46 +678,42 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+          <t>https://koreha.careerlink.kr/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>복지</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026년 한국법무보호복지공단 서울지부 취업지원직(육아휴직대체직) 경력경쟁채용시험 공고</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 노원구</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -717,59 +721,47 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>- 임용예정일에 근무가 가능한 자 - 공고일 기준 만 18세 이상 및 만 60세 이하(공단 정년) - 남성의 경우 「병역법」에 따라 병역의무 불이행 사실이 없는 자 - 성별 ? 학력 ? 거주지 제한 없음 - 공단 규정에 따라 비상대기 및 출동 가능한 자 - 공단 인사규정 등에 의한 임용결격사유에 해당되지 않는 자 [취업지원직 자격요건] 아래 자격증 중 1개 이상 취득한 자 ①직업상담사 2급 이상 ②사회복지사 2급 이상 ③청소년상담사 2급 이상</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>가. 장애인 : 서류전형 만점의 5% - 「장애인 고용촉진 및 직업재활법 시행령」에 의한 장애인 나. 공단 체험형 청년인턴 : 서류전형 만점의 1% ~ 2% - 우리 공단 체험형 청년인턴으로 6개월 이상 근무하여 수료한 경우 수료일로부터 2년 이내 서류전형 만점의 2%(공고문 참고) 다. 가산특전 적용 유의사항 - 가산특전은 서류전형 점수에만 적용 - 장애인 가산특전은 타 가산특전과 중복 적용 가능 - 응시자의 서류전형 점수가 만점의 40% 미만일 경우 적용 제외 - 세부 참조 사항은 공고문 참조 장애인, 한국법무보호복지공단 체험형</t>
-        </is>
-      </c>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://recruit.incruit.com/koreha</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026년 한국법무보호복지공단 신입직원 공개(경력)경쟁채용시험 공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -779,130 +771,386 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,울산,경기,강원,충북,충남,전북,전남광주,경북,경남,제주</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;공통 응시자격&gt; - 임용예정일에 근무 가능한 자 - 만 18세 이상 및 60세 이하(공단 정년) - 남성의 경우, 「병역법」에 따라 병역의무 불이행 사실이 없는 자 - 성별 · 학력 · 거주지 제한 없음 - 공단 규정에 따라 전국 순환근무, 비상대기 · 출동 가능한 자 - 공단 인사규정 등에 의한 임용결격사유에 해당되지 않는 자 ※【별첨 1】임용 결격사유 &lt;심리상담직&gt; - 다음 자격증 중 1개 이상의 자격증을 취득한 사람 ① 정신건강임상심리사 2급 이상 ② 상담심리사 2급 이상(※ 한국상담심리학회) ③ 임상심리사 2급 이상 ④ 전문상담사 2급 이상(※ 한국상담학회) &lt;취업지원직&gt; - 다음 자격증 중 1개 이상의 자격증을 취득하고, 이후 취업지원업무 수행 경력 1년 이상인 자 ① 직업상담사 2급 이상 ② 사회복지사 2급 이상 ③ 청소년상담사 2급 이상 &lt;직업훈련교사직(전기)&gt; - 「국민평생직업능력개발법」 제33조에 따른 직업능력개발훈련교사 3급(전기·전기공사) 이상 소지자</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>가산특전 1) 취업지원대상자 : 5% 또는 10%로 보호직(전국), 취업지원직 모집에 한함 2) 직무관련자격증 : 3% 또는 5%로 보호직에만 적용 3) 장애인 : 5%로 전 채용분야에 적용 4) 한국사능력검정시험 등급 소지자 : 1% 또는 1.5% 또는 2%로 전 채용분야에 적용 5) 한국법무보호복지공단 체험형 청년인턴 : 1% 또는 2%로 전 채용분야에 적용 * 상세사항 공고문 참조 업지원대상자, 직무 관련 자격증, 장애인, 한국사능력검정시험 등급 소지자, 한국법무보호복지공단 체험형 청년인턴 경력</t>
-        </is>
-      </c>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://koreha.careerlink.kr/</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>청소년 · 복지 · 행정</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>국가아동권리보장원</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>서울,경기</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(4년)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 행정</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>건설근로자공제회</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>학력무관,고졸</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>D-13</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>잡알리오(공공기관)</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>https://cw.careerlink.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>한국청소년상담복지개발원</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>D-3</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>이음</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>임상심리치료전문인력 채용</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
+++ b/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -685,189 +685,209 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>청소년 · 복지 · 행정</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>성모자애드림힐 임상심리사 채용 재공고</t>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>정규직,비정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 노원구</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>서울,경기</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(4년)</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://cw.careerlink.kr</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
+          <t>상담 · 청소년 · 복지</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>무기계약직,비정규직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
+          <t>경기</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>학력무관,대졸(4년)</t>
+          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-3</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
+          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
+          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -877,280 +897,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 행정</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>건설근로자공제회</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,고졸</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>잡알리오(공공기관)</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://cw.careerlink.kr</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>상담 · 청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>한국청소년상담복지개발원</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>무기계약직,비정규직</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>D-3</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>잡알리오(공공기관)</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
           <t>https://kyci.fairyhr.com/announcement/detail/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>이음</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>임상심리치료전문인력 채용</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>경기도 시흥시</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>D-11</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>상담</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>경기도 수원시</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>복지넷</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
+++ b/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -685,224 +685,472 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 행정</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>성모자애드림힐</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+          <t>성모자애드림힐 임상심리사 채용 재공고</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>정규직,비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>서울,경기</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,대졸(4년)</t>
-        </is>
-      </c>
+          <t>서울특별시 노원구</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-10</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
-        </is>
-      </c>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1064131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>건설근로자공제회</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>학력무관,고졸</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
-        </is>
-      </c>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://cw.careerlink.kr</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지</t>
+          <t>청소년 · 복지 · 행정</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>국가아동권리보장원</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>서울,경기</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(4년)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>[공통 응시자격] - 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가) - 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자 - 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자 - 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자 [채용분야 응시자격] ○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당 다음 각 자격요건 중 하나 이상에 해당하는 자 - 국가 또는 지방공무원 4급직 이상에 재직한 자 - 국가 또는 지방공무원 5급에 5년 이상 재직한 자 - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자 - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자 ○ 사업관리(입</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>○ 가점 적용 &lt;공통&gt; - 취업지원대상자: 전형별 만점의 5% 또는 10% - 장애인 1) 심한 장애: 전형별 만점의 10% 2) 심하지 않은 장애: 전형별 만점의 5% - 자립준비청년: 전형별 만점의 5% - 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2% &lt;정규직 채용 분야&gt; - 비수도권지역인재: 서류전형 만점의 5% - 고졸자: 서류전형 만점의 5% - 청년인턴 근무경력자: 서류전형 만점의 2%(우수인턴수료자 1% 가산) - 보장원 근무경력자(채용 공고일을 기준으로 3년 이내에 보장원에 근무한 경력, 2회 이</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 행정</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>건설근로자공제회</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026년 건설근로자공제회 제2차 채용공고[일반직(6급, 7급), 무기직(기능직, 상담직), 휴직대체(기간제), 체험형 청년인턴]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직,비정규직,청년인턴(체험형)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>서울,부산,대구,인천,대전,경기,강원,전북,전남광주,제주</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1. 공통자격 ㅇ 성별·어학성적 : 제한 없음 ㅇ 연령 : 당사의 정년(만 60세)에 도달하지 않는 자(입사지원서 접수 마감일 기준) ㅇ 공제회 인사규정 제22조(결격사유)에 해당하지 않는 자 ㅇ 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자 ㅇ 해당분야 직무 수행이 가능한 자 ㅇ 전 분야별(직군?채용분야 및 근무지) 중복지원 불가(중복지원 확인 시 서류전형 불합격 처리) 2. 세부자격 ㅇ (일반직 6급) 일반행정(일반) - 공통 자격 요건 이외 제한 없음 ㅇ (일반직 6급) 일반행정(보훈) - ?국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 ㅇ (일반직 7급) 일반행정(일반) - 고등학교 졸업자(입사지원서 접수 마감일 기준) 주1) 고등학교 검정고시 합격자 및 대학 중퇴자는 지원 가능 주2) 고등학교 졸업예정자, 대학(전문대 포함) 졸업(예정)자·재학생·휴학생 등 지원 불가 ㅇ (무기계약직_기능직(L5)) 차량운전원 -제1종 대형 운</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅇ 국가유공자 등 예우 및 지원에 관한 법률? 등 보훈관계법률에 따른 취업지원대상자 가점(서류, 필기, 면접) ㅇ 장애인 고용촉진 및 직업 재활법 시행령? 제3조에 해당하는 자 가점(서류, 필기) ㅇ 공제회에서 인턴을 수료한 자 또는 공제회와 근로계약을 체결한 비정규직으로 6개월 이상 근로한 자 가점(서류) ㅇ 「국민기초생활 보장법」 제2조 제2호에 따른 기초생활수급자(서류) ㅇ 공고마감일 기준 「아동복지법」에 따른 보호조치가 종료되거나 보호시설을 퇴소한 자(서류) ㅇ「북한이탈주민의 보호 및 정착지원에 관한 법률」 제2조 제1호에 </t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://cw.careerlink.kr</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>한국청소년상담복지개발원</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>제2026-3호 국립중앙청소년디딤센터 직원(공무직, 기간제(휴직대체)) 모집</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>무기계약직,비정규직</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>학력무관,중졸이하,고졸,대졸(2~3년),대졸(4년),석사,박사</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>D-3</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>[공무직] ○ 기관운영지원직 다급 운전분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 환경보안관리직 경비분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 [기간제 휴직대체] ○ 일반직 5급(휴직대체) 치료재활분야(A) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 일반직 5급(휴직대체) 치료재활분야(B) 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조 ○ 보호자립지원직 다급(휴직대체) 프로그램운영분야 1명 - 응시자격 및 근무형태, 업무내용 등은 공고문 및 직무기술명세서 참조</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조) 장애인, 국가유공자, 저소득층, 한부모가족, 북한이탈주민, 다문화가족, 한국사능력, 지역인재 등(상세사항 첨부파일 채용공고문 참조)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>잡알리오(공공기관)</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://kyci.fairyhr.com/announcement/detail/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>이음</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>임상심리치료전문인력 채용</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>상담</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>경기도 수원시</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
+++ b/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>

--- a/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
+++ b/docs/files/2026-09-18/상담행정공고_2026-09-18.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$10</definedName>
